--- a/data/trans_orig/P15B_tráfico-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P15B_tráfico-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>33,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>68,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1793</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7715</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>44,48%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>16,93%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>72,87%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>21955</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>15602</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>27912</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>49,56%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>35,22%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7652</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,48%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>72,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>21955</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>15292</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>28622</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>49,56%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>22269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>66,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2872</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8794</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>55,52%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>83,07%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>22347</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>16390</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>28700</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>50,44%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>37,0%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>64,78%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5878</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2935</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8805</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>55,52%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>83,17%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>22347</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>15680</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>29010</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>50,44%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>35,39%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>24354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17512</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29031</t>
+          <t>29081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42736</t>
+          <t>42711</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17408</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>15537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26525</t>
+          <t>26182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>850</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>20629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>50560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46470</t>
+          <t>47830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>75745</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70580</t>
+          <t>72517</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93001</t>
+          <t>93620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65804</t>
+          <t>65075</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>80931</t>
+          <t>81071</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>143456</t>
+          <t>141138</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>170413</t>
+          <t>169053</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30968</t>
+          <t>31240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49518</t>
+          <t>49442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24673</t>
+          <t>25719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39838</t>
+          <t>40467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>23126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>40922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59396</t>
+          <t>59124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30645</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43670</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51675</t>
+          <t>53321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69297</t>
+          <t>69296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31514</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76679</t>
+          <t>77612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96794</t>
+          <t>97212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25147</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15307</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>32858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31419</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46377</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53273</t>
+          <t>53096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70647</t>
+          <t>69967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>29040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36188</t>
+          <t>36203</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>22649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32791</t>
+          <t>32851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55667</t>
+          <t>55075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68029</t>
+          <t>68014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30512</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>39722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>40982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51494</t>
+          <t>51564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31205</t>
+          <t>31478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41605</t>
+          <t>40662</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46500</t>
+          <t>47567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66521</t>
+          <t>66465</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75116</t>
+          <t>75124</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59210</t>
+          <t>57422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89346</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>35480</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61910</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102019</t>
+          <t>103161</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>141291</t>
+          <t>144262</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>197626</t>
+          <t>197917</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>227762</t>
+          <t>229550</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>193988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>219489</t>
+          <t>219925</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>401086</t>
+          <t>398115</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>440358</t>
+          <t>439216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18525</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26308</t>
+          <t>26094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>23590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36111</t>
+          <t>35922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34878</t>
+          <t>35092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48785</t>
+          <t>48640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>21413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>15255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>31937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30160</t>
+          <t>29444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42983</t>
+          <t>42758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42647</t>
+          <t>41599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58651</t>
+          <t>58281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22321</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>31410</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>23239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>39410</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52166</t>
+          <t>52766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>27784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33777</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46935</t>
+          <t>46643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -8063,62 +8063,62 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7649</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,13%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>54,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7583</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4901</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>54,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4194</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,49 +8191,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>29381</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>25457</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>30358</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>83,86%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29381</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>26164</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>86,18%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>35</t>
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34517</t>
+          <t>34642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43334</t>
+          <t>43300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23956</t>
+          <t>23793</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34987</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35276</t>
+          <t>34737</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47962</t>
+          <t>48544</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31443</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54840</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44404</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>61994</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92239</t>
+          <t>91738</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142929</t>
+          <t>141268</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>166326</t>
+          <t>166166</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147049</t>
+          <t>147234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167875</t>
+          <t>168338</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>296984</t>
+          <t>297485</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>328808</t>
+          <t>327229</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>18823</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29731</t>
+          <t>29741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11387</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>79,08%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>751</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>18944</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13981</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>26337</t>
+          <t>31253</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17397</t>
+          <t>21686</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34107</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>48533</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>48533</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>48533</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19731</t>
+          <t>21160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31432</t>
+          <t>33792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24021</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29484</t>
+          <t>30758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>41269</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>35224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48736</t>
+          <t>51520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,65%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37002</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37002</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37002</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>65037</t>
+          <t>69016</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65037</t>
+          <t>69016</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65037</t>
+          <t>69016</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>24726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25740</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>37873</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>30097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>44309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25730</t>
+          <t>27670</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>23529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27787</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>61765</t>
+          <t>65543</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53414</t>
+          <t>57192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68119</t>
+          <t>73112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>54823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>54823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>54823</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>79154</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>79154</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79154</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19296</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>19319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>28211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>30545</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23986</t>
+          <t>26267</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>34122</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>51322</t>
+          <t>54972</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>47939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55704</t>
+          <t>59966</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>69800</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>69800</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>69800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>30841</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>27028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>33546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>42002</t>
+          <t>45165</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38116</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44940</t>
+          <t>48875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,22 +11758,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -11836,27 +11836,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20391</t>
+          <t>22668</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>21049</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>50239</t>
+          <t>53646</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47055</t>
+          <t>49932</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51890</t>
+          <t>55520</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>70630</t>
+          <t>76314</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67210</t>
+          <t>72852</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72567</t>
+          <t>78439</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>46168</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70825</t>
+          <t>76711</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60207</t>
+          <t>66540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>110382</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81571</t>
+          <t>90501</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121571</t>
+          <t>131372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>145904</t>
+          <t>160554</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>128305</t>
+          <t>143200</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>159605</t>
+          <t>173743</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>166630</t>
+          <t>181155</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153396</t>
+          <t>165640</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>177633</t>
+          <t>193420</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>312534</t>
+          <t>341709</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>291162</t>
+          <t>320719</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>331162</t>
+          <t>361590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
